--- a/employment_forms/027_customer_service_communication_skills_employment_form--employment_forms.xlsx
+++ b/employment_forms/027_customer_service_communication_skills_employment_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'10+_years'}</t>
+          <t>10+_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '10+ years'}</t>
+          <t>10+ years</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'not_specified'}</t>
+          <t>not_specified</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Not Specified'}</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active_listening'}</t>
+          <t>active_listening</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active Listening'}</t>
+          <t>Active Listening</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'conflict_resolution'}</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Conflict Resolution'}</t>
+          <t>Conflict Resolution</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'emotional_intelligence'}</t>
+          <t>emotional_intelligence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Emotional Intelligence'}</t>
+          <t>Emotional Intelligence</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'negotiation'}</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Negotiation'}</t>
+          <t>Negotiation</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'persuasion'}</t>
+          <t>persuasion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Persuasion'}</t>
+          <t>Persuasion</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'public_speaking'}</t>
+          <t>public_speaking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Public Speaking'}</t>
+          <t>Public Speaking</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'writing'}</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Writing'}</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
